--- a/data/2-1.xlsx
+++ b/data/2-1.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D309BC-DD91-4F3A-83B8-CF76E6160799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mhlwlan-my.sharepoint.com/personal/khcpt_lansys_mhlw_go_jp/Documents/PassageDrive/PCfolder/Downloads/数式削除後/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{12406A48-BA39-4AF7-B96B-8F5AED79209E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76ECF02A-640C-4DE8-BC04-014E00D4EFCC}"/>
   <bookViews>
-    <workbookView xWindow="30960" yWindow="3345" windowWidth="21600" windowHeight="11385" xr2:uid="{693BC6FF-05D7-4F9A-80D2-58F2DA3CA19E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{831E7A10-FD07-4E32-A10B-2FCE0CFE400C}"/>
   </bookViews>
   <sheets>
     <sheet name="2-1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2-1'!$A$1:$M$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2-1'!$A$1:$M$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -108,15 +113,15 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>昭和35</t>
+    <t>昭和35　</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>平成2</t>
+    <t>平成2　</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>令和元</t>
+    <t>令和元　</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -606,7 +611,7 @@
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -700,6 +705,9 @@
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -788,10 +796,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="桁区切り 2" xfId="2" xr:uid="{EF71CF47-982A-46BA-A8BB-E6F584D2B810}"/>
+    <cellStyle name="桁区切り 2" xfId="2" xr:uid="{7CA51CD0-21F3-4C46-8179-2EC2B58A4C9B}"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 3 2" xfId="1" xr:uid="{7FFFD47C-9E4A-411E-86F3-60486BA8A47E}"/>
-    <cellStyle name="標準 6 3" xfId="3" xr:uid="{F12E3FF2-B298-4ED0-ABD1-E51EE0F746BD}"/>
+    <cellStyle name="標準 3 2" xfId="1" xr:uid="{7B8F554A-30D8-4DBE-A2B3-4DB1DF7C6955}"/>
+    <cellStyle name="標準 6 3" xfId="3" xr:uid="{83A8AAE4-DE77-4D54-B5DA-7948B61B214B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1102,14 +1110,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CDDC6B-8D70-4B5D-B0F5-B1EE0C09EDC4}">
-  <dimension ref="B1:L37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51548552-236A-452F-990F-E9A415C302FB}">
+  <dimension ref="B1:L38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="10" style="9" customWidth="1"/>
-    <col min="3" max="6" width="9.625" style="54" customWidth="1"/>
-    <col min="7" max="12" width="14" style="54" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="9" customWidth="1"/>
+    <col min="3" max="6" width="9.625" style="55" customWidth="1"/>
+    <col min="7" max="12" width="14" style="55" customWidth="1"/>
     <col min="13" max="14" width="1.625" style="9" customWidth="1"/>
     <col min="15" max="256" width="9" style="9"/>
     <col min="257" max="257" width="1.625" style="9" customWidth="1"/>
@@ -1523,28 +1531,28 @@
       <c r="L2" s="7"/>
     </row>
     <row r="3" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="59" t="s">
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="58"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61" t="s">
+      <c r="H3" s="59"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="58"/>
-      <c r="L3" s="62"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="63"/>
     </row>
     <row r="4" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="56"/>
+      <c r="B4" s="57"/>
       <c r="C4" s="10" t="s">
         <v>6</v>
       </c>
@@ -1645,7 +1653,7 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="25">
@@ -1855,7 +1863,7 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="32" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="25">
@@ -1981,7 +1989,7 @@
       <c r="H16" s="26">
         <v>52038560</v>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="33">
         <v>8285332</v>
       </c>
       <c r="J16" s="28">
@@ -1995,10 +2003,10 @@
       </c>
     </row>
     <row r="17" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="33">
+      <c r="B17" s="34">
         <v>18</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="35">
         <v>1085</v>
       </c>
       <c r="D17" s="26">
@@ -2010,7 +2018,7 @@
       <c r="F17" s="30">
         <v>81</v>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="36">
         <v>60531820</v>
       </c>
       <c r="H17" s="26">
@@ -2019,7 +2027,7 @@
       <c r="I17" s="30">
         <v>8319402</v>
       </c>
-      <c r="J17" s="35">
+      <c r="J17" s="36">
         <v>60291</v>
       </c>
       <c r="K17" s="26">
@@ -2030,13 +2038,13 @@
       </c>
     </row>
     <row r="18" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="33">
+      <c r="B18" s="34">
         <v>19</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="35">
         <v>1093</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="37">
         <v>529</v>
       </c>
       <c r="E18" s="27">
@@ -2045,7 +2053,7 @@
       <c r="F18" s="31">
         <v>82</v>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="36">
         <v>63180531</v>
       </c>
       <c r="H18" s="26">
@@ -2054,7 +2062,7 @@
       <c r="I18" s="30">
         <v>8382083</v>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="36">
         <v>62493</v>
       </c>
       <c r="K18" s="26">
@@ -2064,14 +2072,14 @@
         <v>17390</v>
       </c>
     </row>
-    <row r="19" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="33">
+    <row r="19" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="34">
         <v>20</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="35">
         <v>1036</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="37">
         <v>524</v>
       </c>
       <c r="E19" s="27">
@@ -2080,7 +2088,7 @@
       <c r="F19" s="31">
         <v>84</v>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="36">
         <v>63336217</v>
       </c>
       <c r="H19" s="26">
@@ -2089,7 +2097,7 @@
       <c r="I19" s="30">
         <v>7928000</v>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="36">
         <v>66530</v>
       </c>
       <c r="K19" s="26">
@@ -2099,14 +2107,14 @@
         <v>18523</v>
       </c>
     </row>
-    <row r="20" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="33">
+    <row r="20" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="34">
         <v>21</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="35">
         <v>934</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="37">
         <v>455</v>
       </c>
       <c r="E20" s="27">
@@ -2115,7 +2123,7 @@
       <c r="F20" s="31">
         <v>81</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="36">
         <v>59711941</v>
       </c>
       <c r="H20" s="26">
@@ -2124,7 +2132,7 @@
       <c r="I20" s="30">
         <v>8010546</v>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="36">
         <v>70002</v>
       </c>
       <c r="K20" s="26">
@@ -2134,14 +2142,14 @@
         <v>20127</v>
       </c>
     </row>
-    <row r="21" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="33">
+    <row r="21" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="34">
         <v>22</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <v>947</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="37">
         <v>455</v>
       </c>
       <c r="E21" s="27">
@@ -2150,7 +2158,7 @@
       <c r="F21" s="31">
         <v>79</v>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="36">
         <v>64979554</v>
       </c>
       <c r="H21" s="26">
@@ -2159,7 +2167,7 @@
       <c r="I21" s="30">
         <v>8160135</v>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="36">
         <v>68616</v>
       </c>
       <c r="K21" s="26">
@@ -2169,14 +2177,14 @@
         <v>19758</v>
       </c>
     </row>
-    <row r="22" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="33">
+    <row r="22" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="34">
         <v>23</v>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="39">
         <v>963</v>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="37">
         <v>455</v>
       </c>
       <c r="E22" s="27">
@@ -2185,7 +2193,7 @@
       <c r="F22" s="31">
         <v>88</v>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="36">
         <v>66798724</v>
       </c>
       <c r="H22" s="26">
@@ -2194,7 +2202,7 @@
       <c r="I22" s="30">
         <v>8197839</v>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="36">
         <v>69365</v>
       </c>
       <c r="K22" s="26">
@@ -2204,11 +2212,11 @@
         <v>19519</v>
       </c>
     </row>
-    <row r="23" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="24">
         <v>24</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <v>920</v>
       </c>
       <c r="D23" s="28">
@@ -2220,7 +2228,7 @@
       <c r="F23" s="30">
         <v>86</v>
       </c>
-      <c r="G23" s="38">
+      <c r="G23" s="39">
         <v>61736772</v>
       </c>
       <c r="H23" s="26">
@@ -2229,7 +2237,7 @@
       <c r="I23" s="30">
         <v>8110868</v>
       </c>
-      <c r="J23" s="38">
+      <c r="J23" s="39">
         <v>74025</v>
       </c>
       <c r="K23" s="28">
@@ -2239,11 +2247,11 @@
         <v>20328</v>
       </c>
     </row>
-    <row r="24" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="24">
         <v>25</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="35">
         <v>969</v>
       </c>
       <c r="D24" s="28">
@@ -2255,7 +2263,7 @@
       <c r="F24" s="30">
         <v>87</v>
       </c>
-      <c r="G24" s="38">
+      <c r="G24" s="39">
         <v>67829375</v>
       </c>
       <c r="H24" s="26">
@@ -2264,7 +2272,7 @@
       <c r="I24" s="30">
         <v>8182812</v>
       </c>
-      <c r="J24" s="38">
+      <c r="J24" s="39">
         <v>76904</v>
       </c>
       <c r="K24" s="28">
@@ -2274,14 +2282,14 @@
         <v>19030</v>
       </c>
     </row>
-    <row r="25" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="24">
         <v>26</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="35">
         <v>955</v>
       </c>
-      <c r="D25" s="36">
+      <c r="D25" s="37">
         <v>448</v>
       </c>
       <c r="E25" s="27">
@@ -2290,7 +2298,7 @@
       <c r="F25" s="31">
         <v>86</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="36">
         <v>64325263</v>
       </c>
       <c r="H25" s="26">
@@ -2299,7 +2307,7 @@
       <c r="I25" s="30">
         <v>8125253</v>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="36">
         <v>74022</v>
       </c>
       <c r="K25" s="26">
@@ -2309,14 +2317,14 @@
         <v>19300</v>
       </c>
     </row>
-    <row r="26" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="24">
         <v>27</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="35">
         <v>976</v>
       </c>
-      <c r="D26" s="36">
+      <c r="D26" s="37">
         <v>474</v>
       </c>
       <c r="E26" s="27">
@@ -2325,7 +2333,7 @@
       <c r="F26" s="31">
         <v>86</v>
       </c>
-      <c r="G26" s="35">
+      <c r="G26" s="36">
         <v>66628539</v>
       </c>
       <c r="H26" s="26">
@@ -2334,7 +2342,7 @@
       <c r="I26" s="30">
         <v>8409584</v>
       </c>
-      <c r="J26" s="35">
+      <c r="J26" s="36">
         <v>68267</v>
       </c>
       <c r="K26" s="26">
@@ -2344,14 +2352,14 @@
         <v>20215</v>
       </c>
     </row>
-    <row r="27" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="24">
         <v>28</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="35">
         <v>938</v>
       </c>
-      <c r="D27" s="36">
+      <c r="D27" s="37">
         <v>457</v>
       </c>
       <c r="E27" s="27">
@@ -2360,7 +2368,7 @@
       <c r="F27" s="31">
         <v>83</v>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="36">
         <v>66356514</v>
       </c>
       <c r="H27" s="26">
@@ -2369,7 +2377,7 @@
       <c r="I27" s="30">
         <v>7830516</v>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="36">
         <v>70743</v>
       </c>
       <c r="K27" s="26">
@@ -2379,14 +2387,14 @@
         <v>19675</v>
       </c>
     </row>
-    <row r="28" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="24">
         <v>29</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="35">
         <v>895</v>
       </c>
-      <c r="D28" s="36">
+      <c r="D28" s="37">
         <v>412</v>
       </c>
       <c r="E28" s="27">
@@ -2395,7 +2403,7 @@
       <c r="F28" s="31">
         <v>82</v>
       </c>
-      <c r="G28" s="35">
+      <c r="G28" s="36">
         <v>66197585</v>
       </c>
       <c r="H28" s="26">
@@ -2404,7 +2412,7 @@
       <c r="I28" s="30">
         <v>7716222</v>
       </c>
-      <c r="J28" s="35">
+      <c r="J28" s="36">
         <v>73964</v>
       </c>
       <c r="K28" s="26">
@@ -2414,14 +2422,14 @@
         <v>19242</v>
       </c>
     </row>
-    <row r="29" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="24">
         <v>30</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="35">
         <v>898</v>
       </c>
-      <c r="D29" s="36">
+      <c r="D29" s="37">
         <v>424</v>
       </c>
       <c r="E29" s="27">
@@ -2430,7 +2438,7 @@
       <c r="F29" s="31">
         <v>78</v>
       </c>
-      <c r="G29" s="35">
+      <c r="G29" s="36">
         <v>66518274</v>
       </c>
       <c r="H29" s="26">
@@ -2439,7 +2447,7 @@
       <c r="I29" s="30">
         <v>7828368</v>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="36">
         <v>74074</v>
       </c>
       <c r="K29" s="26">
@@ -2449,14 +2457,14 @@
         <v>19769</v>
       </c>
     </row>
-    <row r="30" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="24" t="s">
+    <row r="30" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>912</v>
       </c>
-      <c r="D30" s="36">
+      <c r="D30" s="37">
         <v>424</v>
       </c>
       <c r="E30" s="27">
@@ -2465,7 +2473,7 @@
       <c r="F30" s="31">
         <v>77</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="36">
         <v>67674062</v>
       </c>
       <c r="H30" s="26">
@@ -2474,7 +2482,7 @@
       <c r="I30" s="30">
         <v>7855767</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="36">
         <v>74204</v>
       </c>
       <c r="K30" s="26">
@@ -2484,14 +2492,14 @@
         <v>19114</v>
       </c>
     </row>
-    <row r="31" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="24">
         <v>2</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="35">
         <v>866</v>
       </c>
-      <c r="D31" s="36">
+      <c r="D31" s="37">
         <v>409</v>
       </c>
       <c r="E31" s="27">
@@ -2500,7 +2508,7 @@
       <c r="F31" s="31">
         <v>73</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="36">
         <v>67613563</v>
       </c>
       <c r="H31" s="26">
@@ -2509,7 +2517,7 @@
       <c r="I31" s="30">
         <v>7569600</v>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="36">
         <v>78076</v>
       </c>
       <c r="K31" s="26">
@@ -2519,14 +2527,14 @@
         <v>19713</v>
       </c>
     </row>
-    <row r="32" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="33">
+    <row r="32" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="24">
         <v>3</v>
       </c>
-      <c r="C32" s="34">
+      <c r="C32" s="35">
         <v>906</v>
       </c>
-      <c r="D32" s="36">
+      <c r="D32" s="37">
         <v>426</v>
       </c>
       <c r="E32" s="27">
@@ -2535,7 +2543,7 @@
       <c r="F32" s="31">
         <v>76</v>
       </c>
-      <c r="G32" s="35">
+      <c r="G32" s="36">
         <v>68897525</v>
       </c>
       <c r="H32" s="26">
@@ -2544,7 +2552,7 @@
       <c r="I32" s="30">
         <v>7697047</v>
       </c>
-      <c r="J32" s="35">
+      <c r="J32" s="36">
         <v>83009</v>
       </c>
       <c r="K32" s="26">
@@ -2554,102 +2562,137 @@
         <v>19052</v>
       </c>
     </row>
-    <row r="33" spans="2:12" s="37" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="39">
+    <row r="33" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="24">
         <v>4</v>
       </c>
-      <c r="C33" s="40">
+      <c r="C33" s="35">
         <v>904</v>
       </c>
-      <c r="D33" s="41">
+      <c r="D33" s="37">
         <v>427</v>
       </c>
-      <c r="E33" s="42">
+      <c r="E33" s="27">
         <v>401</v>
       </c>
-      <c r="F33" s="43">
+      <c r="F33" s="31">
         <v>76</v>
       </c>
-      <c r="G33" s="44">
+      <c r="G33" s="36">
         <v>69291844</v>
       </c>
-      <c r="H33" s="45">
+      <c r="H33" s="26">
         <v>61674168</v>
       </c>
-      <c r="I33" s="46">
+      <c r="I33" s="30">
         <v>7617676</v>
       </c>
-      <c r="J33" s="44">
-        <v>83685.801932367147</v>
-      </c>
-      <c r="K33" s="45">
-        <v>144435.99063231851</v>
-      </c>
-      <c r="L33" s="42">
-        <v>18996.698254364092</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" s="37" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="47"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-    </row>
-    <row r="35" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="48" t="s">
+      <c r="J33" s="36">
+        <v>83686</v>
+      </c>
+      <c r="K33" s="26">
+        <v>144436</v>
+      </c>
+      <c r="L33" s="27">
+        <v>18997</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="40">
+        <v>5</v>
+      </c>
+      <c r="C34" s="41">
+        <v>897</v>
+      </c>
+      <c r="D34" s="42">
+        <v>425</v>
+      </c>
+      <c r="E34" s="43">
+        <v>396</v>
+      </c>
+      <c r="F34" s="44">
+        <v>76</v>
+      </c>
+      <c r="G34" s="45">
+        <v>69353875</v>
+      </c>
+      <c r="H34" s="46">
+        <v>61818465</v>
+      </c>
+      <c r="I34" s="47">
+        <v>7535410</v>
+      </c>
+      <c r="J34" s="45">
+        <v>84475</v>
+      </c>
+      <c r="K34" s="46">
+        <v>145455</v>
+      </c>
+      <c r="L34" s="43">
+        <v>19029</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" s="38" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="48"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="C36" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="51"/>
-      <c r="K35" s="51"/>
-      <c r="L35" s="51"/>
-    </row>
-    <row r="36" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="52"/>
-      <c r="C36" s="49" t="s">
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
+      <c r="K36" s="52"/>
+      <c r="L36" s="52"/>
+    </row>
+    <row r="37" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="53"/>
+      <c r="C37" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="51"/>
-      <c r="K36" s="51"/>
-      <c r="L36" s="51"/>
-    </row>
-    <row r="37" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="53" t="s">
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="52"/>
+      <c r="L37" s="52"/>
+    </row>
+    <row r="38" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="49" t="s">
+      <c r="C38" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="51"/>
-      <c r="L37" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2660,9 +2703,275 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.59055118110236227" bottom="0.43307086614173229" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="66" firstPageNumber="90" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="60" firstPageNumber="112" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;C&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101004B7A08F41466F54DAD85CC8F8B6DD819" ma:contentTypeVersion="14" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="3ccd3af923fed202da3f605c24f7573a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169140c8-6638-4909-a9c8-859c70515230" xmlns:ns3="263dbbe5-076b-4606-a03b-9598f5f2f35a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f6e36929e29d9ce3d46fe4fa871c352b" ns2:_="" ns3:_="">
+    <xsd:import namespace="169140c8-6638-4909-a9c8-859c70515230"/>
+    <xsd:import namespace="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:Owner" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="169140c8-6638-4909-a9c8-859c70515230" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="Owner" ma:index="8" nillable="true" ma:displayName="所有者" ma:internalName="Owner">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:User">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0347f584-7be2-4218-8e94-402d99aedf0b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="263dbbe5-076b-4606-a03b-9598f5f2f35a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ad13c9aa-c1b7-4fb9-bc19-e9e3d8a0d1dc}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="263dbbe5-076b-4606-a03b-9598f5f2f35a">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
+    <Owner xmlns="169140c8-6638-4909-a9c8-859c70515230">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="169140c8-6638-4909-a9c8-859c70515230">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB5ECB6A-AB4C-42BC-A23D-A51311278EF6}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A51E8DBA-734C-4D55-A581-EB703A3A37F7}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51FC8AFE-8029-4598-9EDA-D3BB1D0E9D3E}"/>
 </file>